--- a/output/pdf_financials_xlsx/RARE.xlsx
+++ b/output/pdf_financials_xlsx/RARE.xlsx
@@ -2508,19 +2508,19 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>5.338148</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>1.354501</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>1.352782</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>1.636377</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>2.078328</v>
       </c>
     </row>
     <row r="93">
@@ -4306,7 +4306,11 @@
           <t>Reserves 6</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr"/>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E21" t="inlineStr">
         <is>
           <t>-</t>
@@ -4794,7 +4798,11 @@
           <t>Reserves 7</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr"/>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E33" t="inlineStr">
         <is>
           <t>-</t>
@@ -5245,7 +5253,11 @@
           <t>Reserves 7</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr"/>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E44" t="inlineStr">
         <is>
           <t>-</t>
@@ -5698,7 +5710,11 @@
           <t>Reserves 6</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr"/>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E55" s="5" t="n">
         <v>5.338148</v>
       </c>

--- a/output/pdf_financials_xlsx/RARE.xlsx
+++ b/output/pdf_financials_xlsx/RARE.xlsx
@@ -631,13 +631,13 @@
         <v>3.61783</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0.28626</v>
+        <v>2.402179</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>0.51348</v>
+        <v>2.035567</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0.6354959999999999</v>
+        <v>2.949397</v>
       </c>
     </row>
     <row r="11">
@@ -653,13 +653,13 @@
         <v>-3.61783</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>-0.28626</v>
+        <v>-2.402179</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>-0.51348</v>
+        <v>-2.035567</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>-0.6354959999999999</v>
+        <v>-2.949397</v>
       </c>
     </row>
     <row r="12">
@@ -1208,19 +1208,19 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>4.617481</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>2.314839</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>1.125043</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.045115</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.064306</v>
       </c>
     </row>
     <row r="35">
@@ -1252,19 +1252,19 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>4.617481</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>2.314839</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>1.125043</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.045115</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.064306</v>
       </c>
     </row>
     <row r="37">
@@ -1516,19 +1516,19 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>4.679693</v>
+        <v>0.062212</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>2.314839</v>
+        <v>0</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>1.125043</v>
+        <v>0</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.045115</v>
+        <v>0</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.064306</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -3582,7 +3582,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" s="5" t="n">
@@ -9609,7 +9609,7 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
@@ -9618,16 +9618,16 @@
         </is>
       </c>
       <c r="F150" s="5" t="n">
-        <v>-3.61783</v>
+        <v>3.61783</v>
       </c>
       <c r="G150" s="5" t="n">
-        <v>-2.402179</v>
+        <v>2.402179</v>
       </c>
       <c r="H150" s="5" t="n">
-        <v>-2.035567</v>
+        <v>2.035567</v>
       </c>
       <c r="I150" s="5" t="n">
-        <v>-2.949397</v>
+        <v>2.949397</v>
       </c>
     </row>
     <row r="151">

--- a/output/pdf_financials_xlsx/RARE.xlsx
+++ b/output/pdf_financials_xlsx/RARE.xlsx
@@ -769,7 +769,7 @@
         <v>-3.592499</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>-6.606298</v>
+        <v>-6.592406</v>
       </c>
     </row>
     <row r="17">
@@ -788,10 +788,10 @@
         <v>-0</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>0.005448</v>
+        <v>-0.005448</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>-0</v>
+        <v>-0.013892</v>
       </c>
     </row>
     <row r="18">
@@ -1061,7 +1061,7 @@
         <v>-3.592499</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-6.606298</v>
+        <v>-6.592406</v>
       </c>
     </row>
     <row r="28">
@@ -1105,7 +1105,7 @@
         <v>-3.589847</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-6.605811</v>
+        <v>-6.591919</v>
       </c>
     </row>
     <row r="30">
@@ -1159,7 +1159,7 @@
         <v>-0.1516493115238167</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>-0</v>
+        <v>-0.2107273126078703</v>
       </c>
     </row>
     <row r="32">
@@ -2691,19 +2691,19 @@
         </is>
       </c>
       <c r="B101" s="3" t="n">
-        <v>0</v>
+        <v>-0.048961</v>
       </c>
       <c r="C101" s="3" t="n">
-        <v>-0.330737</v>
+        <v>-0.375918</v>
       </c>
       <c r="D101" s="3" t="n">
-        <v>0.30924</v>
+        <v>0.34157</v>
       </c>
       <c r="E101" s="3" t="n">
-        <v>0.032091</v>
+        <v>0.033588</v>
       </c>
       <c r="F101" s="3" t="n">
-        <v>-0.007384</v>
+        <v>-0.049923</v>
       </c>
     </row>
     <row r="102">
@@ -2801,19 +2801,19 @@
         </is>
       </c>
       <c r="B106" s="3" t="n">
-        <v>0.201446</v>
+        <v>0.152485</v>
       </c>
       <c r="C106" s="3" t="n">
-        <v>-0.687947</v>
+        <v>-0.733128</v>
       </c>
       <c r="D106" s="3" t="n">
-        <v>0.502194</v>
+        <v>0.534524</v>
       </c>
       <c r="E106" s="3" t="n">
-        <v>2.057231</v>
+        <v>2.058728</v>
       </c>
       <c r="F106" s="3" t="n">
-        <v>4.449419</v>
+        <v>4.40688</v>
       </c>
     </row>
     <row r="107">
@@ -2911,10 +2911,10 @@
         </is>
       </c>
       <c r="B111" s="3" t="n">
-        <v>0</v>
+        <v>-0.006664</v>
       </c>
       <c r="C111" s="3" t="n">
-        <v>0</v>
+        <v>-0.002216</v>
       </c>
       <c r="D111" s="3" t="n">
         <v>0</v>
@@ -3427,10 +3427,10 @@
         </is>
       </c>
       <c r="B134" s="3" t="n">
-        <v>0</v>
+        <v>-0.006664</v>
       </c>
       <c r="C134" s="3" t="n">
-        <v>0</v>
+        <v>-0.002216</v>
       </c>
       <c r="D134" s="3" t="n">
         <v>0</v>
@@ -3449,10 +3449,10 @@
         </is>
       </c>
       <c r="B135" s="3" t="n">
-        <v>-0.798413</v>
+        <v>-0.805077</v>
       </c>
       <c r="C135" s="3" t="n">
-        <v>-2.926878</v>
+        <v>-2.929094</v>
       </c>
       <c r="D135" s="3" t="n">
         <v>-1.776568</v>
@@ -6190,7 +6190,11 @@
           <t>Deferred income tax recovery 5</t>
         </is>
       </c>
-      <c r="D67" t="inlineStr"/>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E67" t="inlineStr">
         <is>
           <t>-</t>
@@ -6229,7 +6233,11 @@
           <t>GST receivable</t>
         </is>
       </c>
-      <c r="D68" t="inlineStr"/>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E68" s="5" t="n">
         <v>-0.048961</v>
       </c>
@@ -7033,7 +7041,11 @@
           <t>Deferred income tax recovery 6</t>
         </is>
       </c>
-      <c r="D88" t="inlineStr"/>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E88" t="inlineStr">
         <is>
           <t>-</t>
@@ -7740,7 +7752,11 @@
           <t>GST receivable</t>
         </is>
       </c>
-      <c r="D105" t="inlineStr"/>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E105" t="inlineStr">
         <is>
           <t>-</t>
@@ -8379,7 +8395,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D120" t="inlineStr"/>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E120" s="5" t="n">
         <v>-0.006664</v>
       </c>
@@ -9765,7 +9785,11 @@
           <t>Deferred income tax recovery 5</t>
         </is>
       </c>
-      <c r="D154" t="inlineStr"/>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E154" t="inlineStr">
         <is>
           <t>-</t>
@@ -10384,7 +10408,11 @@
           <t>Deferred income tax recovery 6</t>
         </is>
       </c>
-      <c r="D169" t="inlineStr"/>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E169" t="inlineStr">
         <is>
           <t>-</t>
@@ -10425,7 +10453,11 @@
           <t>Total income tax recovery</t>
         </is>
       </c>
-      <c r="D170" t="inlineStr"/>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E170" t="inlineStr">
         <is>
           <t>-</t>
